--- a/output/2026-09-02_00_Italia_Abruzzo_Cleaning.xlsx
+++ b/output/2026-09-02_00_Italia_Abruzzo_Cleaning.xlsx
@@ -494,7 +494,6 @@
           <t>0863 509227 / 377 2002391</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Verificata tramite più fonti (sito ufficiale, PagineGialle, Lazioshopping, Virgilio). Vendita e noleggio macchine per pulizia industriale e civile (Fimap, Ketek, TTS, Corazzi), aspiratori, prodotti chimici. Oltre 30 anni di attività, opera in tutte le province abruzzesi. Email generica non trovata.</t>
@@ -527,8 +526,6 @@
           <t>Cleaning</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Verificata (sito ufficiale, Dun &amp; Bradstreet, Confindustria Marmomacchine). Produce e commercializza aspiratori industriali linea Powervak, levigatrici/lucidatrici pavimenti e utensili diamantati. ATTENZIONE: risulta essere PRODUTTORE della propria linea di aspiratori (Powervak), non solo distributore/rivenditore terzi - valutare idoneità come partner distributivo per prodotti Dupuy in quanto potenziale concorrente diretto sul segmento aspiratori. Telefono ed email non reperiti nelle fonti consultate.</t>
@@ -573,7 +570,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Verificata (sito ufficiale, Atoka, Europages, PagineBianche). Attiva dal 1958, riorientata alla pulizia professionale dal 1995. Vendita, noleggio, assistenza macchine e prodotti chimici per pulizia industriale/professionale. P.IVA 01772690689.</t>
+          <t>Verificata (sito ufficiale, Atoka, Europages, PagineBianche). Attiva dal 1958, riorientata alla pulizia professionale dal 1995. Vendita, noleggio, assistenza macchine e prodotti chimici per pulizia industriale/professionale. P.IVA 01772690689. [DUPLICATO — vedi anche: 2026-08-31_21_Italia_Liguria_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -615,7 +612,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rete nazionale Pulimacchine (dal 1984), verificata tramite sito ufficiale con pagina/contatti dedicati al servizio regionale Abruzzo/Pescara (vendita nuovo/usato, noleggio, assistenza, ricambi aspiratori, spazzatrici, lavasciuga). Non ha sede fisica propria in Abruzzo, opera come servizio/rete regionale dedicato: valutare se coerente col profilo di 'distributore locale' richiesto.</t>
+          <t>Rete nazionale Pulimacchine (dal 1984), verificata tramite sito ufficiale con pagina/contatti dedicati al servizio regionale Abruzzo/Pescara (vendita nuovo/usato, noleggio, assistenza, ricambi aspiratori, spazzatrici, lavasciuga). Non ha sede fisica propria in Abruzzo, opera come servizio/rete regionale dedicato: valutare se coerente col profilo di 'distributore locale' richiesto. [DUPLICATO — vedi anche: 2026-08-31_08_Italia_Toscana_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -650,7 +647,6 @@
           <t>0862 319775 / 0862 320988</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Verificata (sito ufficiale, Atoka). Specializzata in commercializzazione attrezzature e prodotti per pulizia industriale, abbigliamento da lavoro e DPI, lubrificanti industriali. Email generica non trovata.</t>
@@ -730,7 +726,6 @@
           <t>085 959790 / 335 6852157</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Verificata (sito ufficiale, PagineGialle, PagineBianche, Kompass, Virgilio). Ferramenta all'ingrosso dal 1985, rivenditore autorizzato Kärcher (promozione dedicata 'Karcher ti rimborsa l'IVA' sul sito). Vende aspiratori/idropulitrici. Telefono aggiornato da fonti di verifica (originale non riportato nella lista grezza). Email generica non trovata.</t>
@@ -810,7 +805,6 @@
           <t>0871 561812</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>Verificata (sito ufficiale, Tellows, FourInfolab). Forniture industriali dal 1974, 2000 mq, circa 25 dipendenti. Confermata vendita di aspiratori industriali per trucioli/polveri/liquidi mono e trifase con filtri HEPA. Email generica non trovata.</t>
